--- a/samples/authorized-entities.example.xlsx
+++ b/samples/authorized-entities.example.xlsx
@@ -512,7 +512,6 @@
           <t>2025-01-06</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -545,7 +544,6 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -578,7 +576,6 @@
           <t>2025-03-17</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -692,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,6 +706,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -716,6 +718,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -739,65 +742,70 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
+          <t>Device Subtype</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
           <t>Serial # or Asset Tag</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Mac Address</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>BIOS FW Ver</t>
         </is>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>Asset Type</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>In Service Date</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="M10" s="1" t="inlineStr">
         <is>
           <t>Decommissioned Date</t>
         </is>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>FenixPyre Installed</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="O10" s="1" t="inlineStr">
         <is>
           <t>DUO Installed</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
+      <c r="P10" s="1" t="inlineStr">
         <is>
           <t>Senteon Installed</t>
         </is>
       </c>
-      <c r="P10" s="1" t="inlineStr">
+      <c r="Q10" s="1" t="inlineStr">
         <is>
           <t>RoboShadow Installed</t>
         </is>
       </c>
-      <c r="Q10" s="1" t="inlineStr">
+      <c r="R10" s="1" t="inlineStr">
         <is>
           <t>Heimdal Installed</t>
         </is>
@@ -826,61 +834,65 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>laptop</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>ASSET-0001</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00:11:22:33:44:55</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>00:11:22:33:44:55, AA:BB:CC:DD:EE:01</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Windows 11 Pro 24H2</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1.20.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>HQ - Suite 200</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>CUI Asset</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -909,61 +921,65 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>ASSET-0002</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>00:11:22:33:44:66</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Windows Server 2022</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2.10.1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>HQ - Server Room</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>CUI Asset</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -992,57 +1008,60 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>network_device</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>ASSET-0003</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>00:11:22:33:44:77</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>FortiOS 7.6.7</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HQ - Server Room</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>SPA</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
